--- a/ЛР2-3_Объем_рынка/Excel/ПС_поисковый_спрос_NotaCode.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ПС_поисковый_спрос_NotaCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A81F61A-0761-446F-91A9-D44EE7A4E264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AB10C7-673B-4A1A-97A1-A02399B25971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,20 @@
     <sheet name="09_Источники" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -829,40 +843,40 @@
                 <c:formatCode>yyyy\-mm</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>45900.916666666664</c:v>
+                  <c:v>45900.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45930.916666666664</c:v>
+                  <c:v>45930.875</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45961.958333333336</c:v>
+                  <c:v>45961.875</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45991.958333333336</c:v>
+                  <c:v>45991.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46022.958333333336</c:v>
+                  <c:v>46022.875</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46053.958333333336</c:v>
+                  <c:v>46053.875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46081.958333333336</c:v>
+                  <c:v>46081.875</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46112.916666666664</c:v>
+                  <c:v>46112.875</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46142.916666666664</c:v>
+                  <c:v>46142.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46173.916666666664</c:v>
+                  <c:v>46173.875</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46203.916666666664</c:v>
+                  <c:v>46203.875</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46234.916666666664</c:v>
+                  <c:v>46234.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1307,14 +1321,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="66.125" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
+    <row r="1" spans="1:8" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1326,7 +1340,7 @@
       <c r="G1" s="22"/>
       <c r="H1" s="22"/>
     </row>
-    <row r="3" spans="1:8" ht="42.75">
+    <row r="3" spans="1:8" ht="40.5">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1334,7 +1348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42.75">
+    <row r="4" spans="1:8" ht="40.5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1342,7 +1356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="57">
+    <row r="5" spans="1:8" ht="54">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1350,7 +1364,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42.75">
+    <row r="6" spans="1:8" ht="40.5">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1358,7 +1372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42.75">
+    <row r="7" spans="1:8" ht="40.5">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -1378,7 +1392,7 @@
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
     </row>
-    <row r="10" spans="1:8" ht="15">
+    <row r="10" spans="1:8" ht="13.9">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1489,7 +1503,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="42.625" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
@@ -1498,7 +1512,7 @@
     <col min="5" max="5" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18">
+    <row r="1" spans="1:5" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>127</v>
       </c>
@@ -1507,7 +1521,7 @@
       <c r="D1" s="22"/>
       <c r="E1" s="22"/>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="27.75">
       <c r="A3" s="3" t="s">
         <v>128</v>
       </c>
@@ -1524,7 +1538,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="57">
+    <row r="4" spans="1:5" ht="54">
       <c r="A4" s="2" t="s">
         <v>133</v>
       </c>
@@ -1535,13 +1549,13 @@
         <v>189</v>
       </c>
       <c r="D4" s="19">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.5">
+    <row r="5" spans="1:5" ht="27">
       <c r="A5" s="2" t="s">
         <v>137</v>
       </c>
@@ -1552,13 +1566,13 @@
         <v>139</v>
       </c>
       <c r="D5" s="19">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="42.75">
+    <row r="6" spans="1:5" ht="40.5">
       <c r="A6" s="2" t="s">
         <v>141</v>
       </c>
@@ -1569,13 +1583,13 @@
         <v>190</v>
       </c>
       <c r="D6" s="19">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.5">
+    <row r="7" spans="1:5" ht="27">
       <c r="A7" s="2" t="s">
         <v>144</v>
       </c>
@@ -1586,13 +1600,13 @@
         <v>139</v>
       </c>
       <c r="D7" s="19">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="42.75">
+    <row r="8" spans="1:5" ht="40.5">
       <c r="A8" s="2" t="s">
         <v>147</v>
       </c>
@@ -1609,7 +1623,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.5">
+    <row r="9" spans="1:5" ht="27">
       <c r="A9" s="2" t="s">
         <v>149</v>
       </c>
@@ -1637,7 +1651,7 @@
         <v>194</v>
       </c>
       <c r="D10" s="20">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E10" t="s">
         <v>195</v>
@@ -1654,7 +1668,7 @@
         <v>194</v>
       </c>
       <c r="D11" s="20">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E11" t="s">
         <v>197</v>
@@ -1671,7 +1685,7 @@
         <v>194</v>
       </c>
       <c r="D12" s="20">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E12" t="s">
         <v>200</v>
@@ -1691,7 +1705,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1699,7 +1713,7 @@
     <col min="4" max="4" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18">
+    <row r="1" spans="1:6" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>31</v>
       </c>
@@ -1709,7 +1723,7 @@
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
     </row>
-    <row r="3" spans="1:6" ht="30">
+    <row r="3" spans="1:6" ht="27.75">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
@@ -1874,7 +1888,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="61.875" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -1888,7 +1902,7 @@
     <col min="10" max="10" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>53</v>
       </c>
@@ -1902,7 +1916,7 @@
       <c r="I1" s="22"/>
       <c r="J1" s="22"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2324,7 +2338,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="55.375" customWidth="1"/>
     <col min="2" max="2" width="19.625" customWidth="1"/>
@@ -2335,7 +2349,7 @@
     <col min="7" max="7" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
+    <row r="1" spans="1:8" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>69</v>
       </c>
@@ -2347,7 +2361,7 @@
       <c r="G1" s="22"/>
       <c r="H1" s="22"/>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="27.75">
       <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
@@ -2372,7 +2386,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="11">
-        <v>45900.916666666664</v>
+        <v>45900.875</v>
       </c>
       <c r="B4" s="13">
         <v>0</v>
@@ -2396,7 +2410,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="11">
-        <v>45930.916666666664</v>
+        <v>45930.875</v>
       </c>
       <c r="B5" s="13">
         <v>27.75</v>
@@ -2417,7 +2431,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="11">
-        <v>45961.958333333336</v>
+        <v>45961.875</v>
       </c>
       <c r="B6" s="13">
         <v>18.2</v>
@@ -2438,7 +2452,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="11">
-        <v>45991.958333333336</v>
+        <v>45991.875</v>
       </c>
       <c r="B7" s="13">
         <v>67</v>
@@ -2459,7 +2473,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="11">
-        <v>46022.958333333336</v>
+        <v>46022.875</v>
       </c>
       <c r="B8" s="13">
         <v>0</v>
@@ -2480,7 +2494,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="11">
-        <v>46053.958333333336</v>
+        <v>46053.875</v>
       </c>
       <c r="B9" s="13">
         <v>27</v>
@@ -2501,7 +2515,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="11">
-        <v>46081.958333333336</v>
+        <v>46081.875</v>
       </c>
       <c r="B10" s="13">
         <v>11.4</v>
@@ -2522,7 +2536,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="11">
-        <v>46112.916666666664</v>
+        <v>46112.875</v>
       </c>
       <c r="B11" s="13">
         <v>18.75</v>
@@ -2543,7 +2557,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="11">
-        <v>46142.916666666664</v>
+        <v>46142.875</v>
       </c>
       <c r="B12" s="13">
         <v>0</v>
@@ -2567,7 +2581,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="11">
-        <v>46173.916666666664</v>
+        <v>46173.875</v>
       </c>
       <c r="B13" s="13">
         <v>0</v>
@@ -2591,7 +2605,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="11">
-        <v>46203.916666666664</v>
+        <v>46203.875</v>
       </c>
       <c r="B14" s="13">
         <v>0</v>
@@ -2615,7 +2629,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="11">
-        <v>46234.916666666664</v>
+        <v>46234.875</v>
       </c>
       <c r="B15" s="13">
         <v>0</v>
@@ -2656,7 +2670,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -2668,7 +2682,7 @@
     <col min="8" max="8" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18">
+    <row r="1" spans="1:12" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>72</v>
       </c>
@@ -2680,7 +2694,7 @@
       <c r="G1" s="22"/>
       <c r="H1" s="22"/>
     </row>
-    <row r="3" spans="1:12" ht="30">
+    <row r="3" spans="1:12" ht="27.75">
       <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
@@ -2714,7 +2728,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="11">
-        <v>45900.916666666664</v>
+        <v>45900.875</v>
       </c>
       <c r="B4" s="6">
         <v>21</v>
@@ -2749,7 +2763,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="11">
-        <v>45930.916666666664</v>
+        <v>45930.875</v>
       </c>
       <c r="B5" s="6">
         <v>17</v>
@@ -2784,7 +2798,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="11">
-        <v>45961.958333333336</v>
+        <v>45961.875</v>
       </c>
       <c r="B6" s="6">
         <v>15</v>
@@ -2819,7 +2833,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="11">
-        <v>45991.958333333336</v>
+        <v>45991.875</v>
       </c>
       <c r="B7" s="6">
         <v>20</v>
@@ -2854,7 +2868,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="11">
-        <v>46022.958333333336</v>
+        <v>46022.875</v>
       </c>
       <c r="B8" s="6">
         <v>32</v>
@@ -2886,7 +2900,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="11">
-        <v>46053.958333333336</v>
+        <v>46053.875</v>
       </c>
       <c r="B9" s="6">
         <v>12</v>
@@ -2915,7 +2929,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="11">
-        <v>46081.958333333336</v>
+        <v>46081.875</v>
       </c>
       <c r="B10" s="6">
         <v>50</v>
@@ -2944,7 +2958,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="11">
-        <v>46112.916666666664</v>
+        <v>46112.875</v>
       </c>
       <c r="B11" s="6">
         <v>52</v>
@@ -2973,7 +2987,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="11">
-        <v>46142.916666666664</v>
+        <v>46142.875</v>
       </c>
       <c r="B12" s="6">
         <v>23</v>
@@ -3002,7 +3016,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="11">
-        <v>46173.916666666664</v>
+        <v>46173.875</v>
       </c>
       <c r="B13" s="6">
         <v>12</v>
@@ -3031,7 +3045,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="11">
-        <v>46203.916666666664</v>
+        <v>46203.875</v>
       </c>
       <c r="B14" s="6">
         <v>18</v>
@@ -3060,7 +3074,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="11">
-        <v>46234.916666666664</v>
+        <v>46234.875</v>
       </c>
       <c r="B15" s="6">
         <v>14</v>
@@ -3106,7 +3120,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="66.75" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
@@ -3118,7 +3132,7 @@
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
+    <row r="1" spans="1:8" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>80</v>
       </c>
@@ -3130,7 +3144,7 @@
       <c r="G1" s="22"/>
       <c r="H1" s="22"/>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="27.75">
       <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
@@ -3159,7 +3173,7 @@
     <row r="4" spans="1:8">
       <c r="A4" s="11">
         <f>'03_Google_Trends'!A4</f>
-        <v>45900.916666666664</v>
+        <v>45900.875</v>
       </c>
       <c r="B4" s="12">
         <f>'03_Google_Trends'!F4</f>
@@ -3189,7 +3203,7 @@
     <row r="5" spans="1:8">
       <c r="A5" s="11">
         <f>'03_Google_Trends'!A5</f>
-        <v>45930.916666666664</v>
+        <v>45930.875</v>
       </c>
       <c r="B5" s="12">
         <f>'03_Google_Trends'!F5</f>
@@ -3219,7 +3233,7 @@
     <row r="6" spans="1:8">
       <c r="A6" s="11">
         <f>'03_Google_Trends'!A6</f>
-        <v>45961.958333333336</v>
+        <v>45961.875</v>
       </c>
       <c r="B6" s="12">
         <f>'03_Google_Trends'!F6</f>
@@ -3249,7 +3263,7 @@
     <row r="7" spans="1:8">
       <c r="A7" s="11">
         <f>'03_Google_Trends'!A7</f>
-        <v>45991.958333333336</v>
+        <v>45991.875</v>
       </c>
       <c r="B7" s="12">
         <f>'03_Google_Trends'!F7</f>
@@ -3279,7 +3293,7 @@
     <row r="8" spans="1:8">
       <c r="A8" s="11">
         <f>'03_Google_Trends'!A8</f>
-        <v>46022.958333333336</v>
+        <v>46022.875</v>
       </c>
       <c r="B8" s="12">
         <f>'03_Google_Trends'!F8</f>
@@ -3309,7 +3323,7 @@
     <row r="9" spans="1:8">
       <c r="A9" s="11">
         <f>'03_Google_Trends'!A9</f>
-        <v>46053.958333333336</v>
+        <v>46053.875</v>
       </c>
       <c r="B9" s="12">
         <f>'03_Google_Trends'!F9</f>
@@ -3339,7 +3353,7 @@
     <row r="10" spans="1:8">
       <c r="A10" s="11">
         <f>'03_Google_Trends'!A10</f>
-        <v>46081.958333333336</v>
+        <v>46081.875</v>
       </c>
       <c r="B10" s="12">
         <f>'03_Google_Trends'!F10</f>
@@ -3369,7 +3383,7 @@
     <row r="11" spans="1:8">
       <c r="A11" s="11">
         <f>'03_Google_Trends'!A11</f>
-        <v>46112.916666666664</v>
+        <v>46112.875</v>
       </c>
       <c r="B11" s="12">
         <f>'03_Google_Trends'!F11</f>
@@ -3399,7 +3413,7 @@
     <row r="12" spans="1:8">
       <c r="A12" s="11">
         <f>'03_Google_Trends'!A12</f>
-        <v>46142.916666666664</v>
+        <v>46142.875</v>
       </c>
       <c r="B12" s="12">
         <f>'03_Google_Trends'!F12</f>
@@ -3429,7 +3443,7 @@
     <row r="13" spans="1:8">
       <c r="A13" s="11">
         <f>'03_Google_Trends'!A13</f>
-        <v>46173.916666666664</v>
+        <v>46173.875</v>
       </c>
       <c r="B13" s="12">
         <f>'03_Google_Trends'!F13</f>
@@ -3459,7 +3473,7 @@
     <row r="14" spans="1:8">
       <c r="A14" s="11">
         <f>'03_Google_Trends'!A14</f>
-        <v>46203.916666666664</v>
+        <v>46203.875</v>
       </c>
       <c r="B14" s="12">
         <f>'03_Google_Trends'!F14</f>
@@ -3489,7 +3503,7 @@
     <row r="15" spans="1:8">
       <c r="A15" s="11">
         <f>'03_Google_Trends'!A15</f>
-        <v>46234.916666666664</v>
+        <v>46234.875</v>
       </c>
       <c r="B15" s="12">
         <f>'03_Google_Trends'!F15</f>
@@ -3542,7 +3556,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -3551,7 +3565,7 @@
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>86</v>
       </c>
@@ -3565,7 +3579,7 @@
       <c r="I1" s="22"/>
       <c r="J1" s="22"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="3" t="s">
         <v>87</v>
       </c>
@@ -3801,7 +3815,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="36.625" customWidth="1"/>
     <col min="2" max="2" width="14.125" customWidth="1"/>
@@ -3813,7 +3827,7 @@
     <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
+    <row r="1" spans="1:8" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>106</v>
       </c>
@@ -3825,7 +3839,7 @@
       <c r="G1" s="22"/>
       <c r="H1" s="24"/>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="27.75">
       <c r="A3" s="3" t="s">
         <v>107</v>
       </c>
@@ -3961,14 +3975,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
+    <row r="1" spans="1:8" ht="17.649999999999999">
       <c r="A1" s="21" t="s">
         <v>113</v>
       </c>
@@ -3980,7 +3994,7 @@
       <c r="G1" s="22"/>
       <c r="H1" s="22"/>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" spans="1:8" ht="13.9">
       <c r="A3" s="3" t="s">
         <v>87</v>
       </c>
@@ -4003,7 +4017,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.5">
+    <row r="5" spans="1:8" ht="27">
       <c r="A5" s="2" t="s">
         <v>116</v>
       </c>
@@ -4057,13 +4071,13 @@
       </c>
       <c r="B9" s="18" t="str">
         <f>TEXT('06_Воронка'!B14,"# ##0")&amp;" — "&amp;TEXT('06_Воронка'!D14,"# ##0")</f>
-        <v xml:space="preserve"> 11 —  720</v>
+        <v>11 — 720</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5">
+    <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
         <v>125</v>
       </c>
